--- a/ministry/부서확인/2027_사역신청_확인_제자양육부.xlsx
+++ b/ministry/부서확인/2027_사역신청_확인_제자양육부.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사역팀 확인" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'사역팀 확인'!$A$1:$N$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'사역팀 확인'!$A$2:$T$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,12 +36,12 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001A3A6B"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="001A3A6B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -63,11 +63,17 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001A3A6B"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <color rgb="005C6070"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -76,7 +82,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="008A8F9A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C3A253"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001A3A6B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFCF0"/>
       </patternFill>
     </fill>
   </fills>
@@ -106,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -120,17 +141,38 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="general" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B21"/>
+  <dimension ref="B2:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -535,68 +577,131 @@
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2. 각 사역팀명이 2027년 실제 명칭과 같은지 확인합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>3. F열 '사역 시간·요일'과 G열 '하는 일'을 채워 주세요 — 대부분 비어 있습니다(2026-09-07 추가, 찬양부 일부만 먼저 확인되어 채워져 있습니다). 성도가 앱에서 사역을 고를 때 이름만 보고는 판단할 수 없어(예: 오병이어 1팀·2팀이 무엇이 다른지) 이번에 함께 걷습니다. 짧게만 적어 주셔도 됩니다(예: '매주 화 오전 10시', '주일 예배 전 주차 안내').</t>
+          <t>2. 표 맨 윗줄에 띠가 넷 있습니다. **회색 띠(A~G열)는 저희가 채운 자료라 보시기만** 하면 되고, **금색 띠(H~T열)가 채워 주실 곳**입니다. 채울 칸은 옅은 노란빛으로 칠해 두었습니다. 가로로 넓어 보이지만 팀 이름(D열)은 늘 왼쪽에 붙어 있으니 어느 줄인지 잃지 않으실 겁니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>4. H열 '필요 인원'은 채워 주시면 좋지만 선택 사항입니다 — 정원을 세거나 막는 데 쓰지 않고, 성도님께 참고로만 보여드립니다. 모르시면 비워 두셔도 됩니다.</t>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>① 이름 확정</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>5. K열 '확정 표기명'에 2027년 최종 명칭을 적어 주세요(그대로면 D열과 동일하게 적어도 됩니다).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>6. L열 '변경여부'는 목록에서 유지 / 이름 수정 / 신설 / 폐지 중 하나를 골라 주세요.</t>
+          <t>H열 '확정 표기명'에 2027년 최종 명칭을 적어 주세요(그대로면 D열과 똑같이 적으셔도 됩니다). I열 '변경여부'는 유지 / 이름 수정 / 신설 / 폐지 중에서 고릅니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>7. M열에 확인하신 분 성함을, N열에는 그 밖에 전달할 내용을 적어 주세요.</t>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>② 언제 — 여섯 칸 (2026-09-10 추가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>성도님이 앱에서 「나는 주일 오전만 됩니다」처럼 조건을 걸어 사역을 찾습니다. 그때 쓰이는 것이 이 여섯 칸입니다 — 문장으로 쓰신 시간은 기계가 읽지 못해 따로 받습니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>색이 칠해진 자리</t>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · J·K·L열 (주일 / 평일 / 토요일) — 해당하는 칸에 O 를 넣어 주세요. 여럿이면 여럿 다 넣습니다.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>▨ 분홍색 행 — 두 원본 문서(인사표·신청서)의 표기가 서로 달라 어느 쪽이 맞는지 확인이 필요한 자리입니다. J열 '확인이 필요한 사유'에 무엇이 다른지 적어 두었습니다.</t>
+          <t xml:space="preserve">  · M·N열 (시작 시각 / 끝 시각) — 24시간 꼴로 적어 주세요. 보기: 05:00, 09:30, 14:00, 20:00.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>▨ 회색 행 — 신청이 아니라 지명으로 맡는 임명직입니다. 성도가 직접 신청하지 않으므로 앱의 신청 목록에는 넣지 않습니다. 이름이 맞는지만 확인해 주세요(시간·요일·인원은 안 채우셔도 됩니다).</t>
+          <t xml:space="preserve">  · O열 (한 사람이 서는 주기) — **팀이 모이는 주기가 아니라, 한 분이 실제로 서는 주기**입니다. 당번을 넷이 돌아가며 서면 팀은 매주라도 한 분은 '매달'입니다. 성도님이 재는 것은 자기 부담입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 모르시거나 정해지지 않았으면 비워 두셔도 됩니다 — 그 팀이 목록에서 사라지지는 않고 '정해진 날 없음 · 때마다 다름'으로 보입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>③ 성도님 화면에 그대로 보일 안내</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · P열 '사역 시간·요일(문장으로)' — 사람이 읽는 한 줄입니다. 보기: '매주 화 오전 10시, 예배 30분 전 모임'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · Q열 '하는 일 — 한 줄' — 이름만 보고는 알 수 없는 것을 적어 주세요(예: 오병이어 1팀·2팀이 무엇이 다른지). 짧게만 적으셔도 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · R열 '필요 인원'은 선택입니다 — 정원을 세거나 신청을 막는 데 쓰지 않고 참고로만 보여드립니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>④ 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>S열에 확인하신 분 성함을, T열에는 그 밖에 전달할 내용을 적어 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>색이 칠해진 자리</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>▨ 분홍색 행 — 두 원본 문서(인사표·신청서)의 표기가 서로 달라 어느 쪽이 맞는지 확인이 필요한 자리입니다. G열 '확인이 필요한 사유'에 무엇이 다른지 적어 두었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>▨ 회색 행 — 신청이 아니라 지명으로 맡는 임명직입니다. 성도가 직접 신청하지 않으므로 앱의 신청 목록에는 넣지 않습니다. 이름이 맞는지만 확인해 주세요(②·③은 안 채우셔도 됩니다).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>문의: 방송전산부 전산팀</t>
         </is>
@@ -613,252 +718,364 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>확인해 주실 자료 (저희가 채웠습니다 · 보기만 하세요)</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>① 이름 확정</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>② 언제 — 성도님이 이 여섯 칸으로 사역을 찾습니다</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>③ 성도님 화면에 그대로 보일 안내</t>
+        </is>
+      </c>
+      <c r="S1" s="7" t="inlineStr">
+        <is>
+          <t>④ 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>순번</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>위원회/부서</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>중분류</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>사역팀명(신청서 표기 초안)</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>사역 시간·요일 (부서 기입)</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>하는 일 — 한 줄 (부서 기입)</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>필요 인원 (참고, 선택 기입)</t>
-        </is>
-      </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>하위 선택 안내</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>확인이 필요한 사유</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
-        <is>
-          <t>확정 표기명 (부서 기입)</t>
-        </is>
-      </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>확정 표기명</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>변경여부</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
-        <is>
-          <t>담당자 확인 (성명)</t>
-        </is>
-      </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>주일</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>평일</t>
+        </is>
+      </c>
+      <c r="L2" s="8" t="inlineStr">
+        <is>
+          <t>토요일</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>시작 시각</t>
+        </is>
+      </c>
+      <c r="N2" s="8" t="inlineStr">
+        <is>
+          <t>끝 시각</t>
+        </is>
+      </c>
+      <c r="O2" s="8" t="inlineStr">
+        <is>
+          <t>한 사람이 서는 주기</t>
+        </is>
+      </c>
+      <c r="P2" s="8" t="inlineStr">
+        <is>
+          <t>사역 시간·요일 (문장으로)</t>
+        </is>
+      </c>
+      <c r="Q2" s="8" t="inlineStr">
+        <is>
+          <t>하는 일 — 한 줄</t>
+        </is>
+      </c>
+      <c r="R2" s="8" t="inlineStr">
+        <is>
+          <t>필요 인원 (선택)</t>
+        </is>
+      </c>
+      <c r="S2" s="8" t="inlineStr">
+        <is>
+          <t>확인하신 분 (성명)</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6" t="n">
+    <row r="3">
+      <c r="A3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>제자양육부</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr"/>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>단계별 제자양육</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr"/>
-      <c r="G2" s="8" t="inlineStr"/>
-      <c r="H2" s="6" t="inlineStr"/>
-      <c r="I2" s="8" t="inlineStr"/>
-      <c r="J2" s="8" t="inlineStr"/>
-      <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="6" t="inlineStr"/>
-      <c r="M2" s="6" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="n">
+      <c r="F3" s="11" t="n"/>
+      <c r="G3" s="11" t="n"/>
+      <c r="H3" s="12" t="n"/>
+      <c r="I3" s="13" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="14" t="n"/>
+      <c r="L3" s="14" t="n"/>
+      <c r="M3" s="15" t="n"/>
+      <c r="N3" s="15" t="n"/>
+      <c r="O3" s="12" t="n"/>
+      <c r="P3" s="12" t="n"/>
+      <c r="Q3" s="12" t="n"/>
+      <c r="R3" s="12" t="n"/>
+      <c r="S3" s="12" t="n"/>
+      <c r="T3" s="12" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>제자양육부</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr"/>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>마더와이즈</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr"/>
-      <c r="G3" s="8" t="inlineStr"/>
-      <c r="H3" s="6" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="8" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="6" t="inlineStr"/>
-      <c r="M3" s="6" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="n">
+      <c r="F4" s="11" t="n"/>
+      <c r="G4" s="11" t="n"/>
+      <c r="H4" s="12" t="n"/>
+      <c r="I4" s="13" t="n"/>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="14" t="n"/>
+      <c r="L4" s="14" t="n"/>
+      <c r="M4" s="15" t="n"/>
+      <c r="N4" s="15" t="n"/>
+      <c r="O4" s="12" t="n"/>
+      <c r="P4" s="12" t="n"/>
+      <c r="Q4" s="12" t="n"/>
+      <c r="R4" s="12" t="n"/>
+      <c r="S4" s="12" t="n"/>
+      <c r="T4" s="12" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>제자양육부</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>5060하프타임</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="8" t="inlineStr"/>
-      <c r="H4" s="6" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr"/>
-      <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="6" t="inlineStr"/>
-      <c r="M4" s="6" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="n">
+      <c r="F5" s="11" t="n"/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="14" t="n"/>
+      <c r="K5" s="14" t="n"/>
+      <c r="L5" s="14" t="n"/>
+      <c r="M5" s="15" t="n"/>
+      <c r="N5" s="15" t="n"/>
+      <c r="O5" s="12" t="n"/>
+      <c r="P5" s="12" t="n"/>
+      <c r="Q5" s="12" t="n"/>
+      <c r="R5" s="12" t="n"/>
+      <c r="S5" s="12" t="n"/>
+      <c r="T5" s="12" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>제자양육부</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>신앙운동</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="6" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="6" t="inlineStr"/>
-      <c r="M5" s="6" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="n">
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="13" t="n"/>
+      <c r="J6" s="14" t="n"/>
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="15" t="n"/>
+      <c r="N6" s="15" t="n"/>
+      <c r="O6" s="12" t="n"/>
+      <c r="P6" s="12" t="n"/>
+      <c r="Q6" s="12" t="n"/>
+      <c r="R6" s="12" t="n"/>
+      <c r="S6" s="12" t="n"/>
+      <c r="T6" s="12" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>제자양육부</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>학사관리</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr"/>
-      <c r="J6" s="8" t="inlineStr"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="6" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="12" t="n"/>
+      <c r="I7" s="13" t="n"/>
+      <c r="J7" s="14" t="n"/>
+      <c r="K7" s="14" t="n"/>
+      <c r="L7" s="14" t="n"/>
+      <c r="M7" s="15" t="n"/>
+      <c r="N7" s="15" t="n"/>
+      <c r="O7" s="12" t="n"/>
+      <c r="P7" s="12" t="n"/>
+      <c r="Q7" s="12" t="n"/>
+      <c r="R7" s="12" t="n"/>
+      <c r="S7" s="12" t="n"/>
+      <c r="T7" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N6"/>
-  <dataValidations count="1">
-    <dataValidation sqref="L2:L6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 골라주세요" prompt="유지 / 이름 수정 / 신설 / 폐지 중 선택" type="list">
+  <autoFilter ref="A2:T7"/>
+  <mergeCells count="5">
+    <mergeCell ref="P1:R1"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="J1:O1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="H1:I1"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation sqref="I3:I7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 골라주세요" prompt="유지 / 이름 수정 / 신설 / 폐지 중 선택" type="list">
       <formula1>"유지,이름 수정,신설,폐지"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J3:J7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="O 만 넣어 주세요" prompt="이 요일에 사역하면 O (아니면 비워 두세요)" type="list">
+      <formula1>"O"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K3:K7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="O 만 넣어 주세요" prompt="이 요일에 사역하면 O (아니면 비워 두세요)" type="list">
+      <formula1>"O"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L3:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="O 만 넣어 주세요" prompt="이 요일에 사역하면 O (아니면 비워 두세요)" type="list">
+      <formula1>"O"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O3:O7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 골라주세요" prompt="한 분이 실제로 서는 주기입니다 (팀이 모이는 주기가 아닙니다)" type="list">
+      <formula1>"매주,격주,매달,그때그때"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ministry/부서확인/2027_사역신청_확인_제자양육부.xlsx
+++ b/ministry/부서확인/2027_사역신청_확인_제자양육부.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사역팀 확인" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'사역팀 확인'!$A$2:$T$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'사역팀 확인'!$A$2:$X$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -127,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -171,8 +171,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -598,7 +601,7 @@
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>② 언제 — 여섯 칸 (2026-09-10 추가)</t>
+          <t>② 언제 — 열 칸 (2026-09-10)</t>
         </is>
       </c>
     </row>
@@ -612,21 +615,21 @@
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · J·K·L열 (주일 / 평일 / 토요일) — 해당하는 칸에 O 를 넣어 주세요. 여럿이면 여럿 다 넣습니다.</t>
+          <t xml:space="preserve">  · J~M열 (주일 / 금요일 / 토요일 / 평일) — 해당하는 칸마다 O. 여럿이면 여럿 다 넣습니다. ⚠️ 금요일은 따로 두었으니 M열 '평일'은 **금요일을 뺀 날**(월~목)로 봐 주세요 — 금요성령집회·행복전도대(금)처럼 금요일 사역이 많아 성도가 금요일만 골라 찾을 수 있게 나눴습니다.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · M·N열 (시작 시각 / 끝 시각) — 24시간 꼴로 적어 주세요. 보기: 05:00, 09:30, 14:00, 20:00.</t>
+          <t xml:space="preserve">  · N~Q열 (매주 / 격주(교대형식) / 매달 / 그때그때) — 해당하는 칸마다 O. **여럿 고를 수 있습니다** (매주 또는 격주인 팀이 있습니다). ⚠️ **팀이 모이는 주기가 아니라, 한 분이 실제로 서는 주기**입니다. 당번을 넷이 돌아가며 서면 팀은 매주라도 한 분은 '매달'입니다 — 성도님이 재는 것은 자기 부담입니다.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · O열 (한 사람이 서는 주기) — **팀이 모이는 주기가 아니라, 한 분이 실제로 서는 주기**입니다. 당번을 넷이 돌아가며 서면 팀은 매주라도 한 분은 '매달'입니다. 성도님이 재는 것은 자기 부담입니다.</t>
+          <t xml:space="preserve">  · R·S열 (주일 시작 시각 / 주일 끝 시각) — 24시간 꼴로. 보기: 09:30, 14:00. ⚠️ **주일 사역에만** 적습니다. 평일·금요일·토요일 사역의 시간은 아래 ③의 문장 칸에 적어 주세요.</t>
         </is>
       </c>
     </row>
@@ -647,21 +650,21 @@
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · P열 '사역 시간·요일(문장으로)' — 사람이 읽는 한 줄입니다. 보기: '매주 화 오전 10시, 예배 30분 전 모임'.</t>
+          <t xml:space="preserve">  · T열 '사역 시간·요일(문장으로)' — 사람이 읽는 한 줄입니다. 보기: '매주 화 오전 10시, 예배 30분 전 모임'. 주일이 아닌 사역의 시간은 여기에 적어 주세요.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Q열 '하는 일 — 한 줄' — 이름만 보고는 알 수 없는 것을 적어 주세요(예: 오병이어 1팀·2팀이 무엇이 다른지). 짧게만 적으셔도 됩니다.</t>
+          <t xml:space="preserve">  · U열 '하는 일 — 한 줄' — 이름만 보고는 알 수 없는 것을 적어 주세요(예: 오병이어 1팀·2팀이 무엇이 다른지). 짧게만 적으셔도 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · R열 '필요 인원'은 선택입니다 — 정원을 세거나 신청을 막는 데 쓰지 않고 참고로만 보여드립니다.</t>
+          <t xml:space="preserve">  · V열 '필요 인원'은 선택입니다 — 정원을 세거나 신청을 막는 데 쓰지 않고 참고로만 보여드립니다.</t>
         </is>
       </c>
     </row>
@@ -675,7 +678,7 @@
     <row r="26">
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>S열에 확인하신 분 성함을, T열에는 그 밖에 전달할 내용을 적어 주세요.</t>
+          <t>W열에 확인하신 분 성함을, X열에는 그 밖에 전달할 내용을 적어 주세요.</t>
         </is>
       </c>
     </row>
@@ -718,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:X7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -731,16 +734,20 @@
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
     <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -756,15 +763,15 @@
       </c>
       <c r="J1" s="7" t="inlineStr">
         <is>
-          <t>② 언제 — 성도님이 이 여섯 칸으로 사역을 찾습니다</t>
-        </is>
-      </c>
-      <c r="P1" s="7" t="inlineStr">
+          <t>② 언제 — 성도님이 이 칸들로 사역을 찾습니다</t>
+        </is>
+      </c>
+      <c r="T1" s="7" t="inlineStr">
         <is>
           <t>③ 성도님 화면에 그대로 보일 안내</t>
         </is>
       </c>
-      <c r="S1" s="7" t="inlineStr">
+      <c r="W1" s="7" t="inlineStr">
         <is>
           <t>④ 확인</t>
         </is>
@@ -823,7 +830,7 @@
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>평일</t>
+          <t>금요일</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
@@ -833,40 +840,60 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>시작 시각</t>
+          <t>평일(금 제외)</t>
         </is>
       </c>
       <c r="N2" s="8" t="inlineStr">
         <is>
-          <t>끝 시각</t>
+          <t>매주</t>
         </is>
       </c>
       <c r="O2" s="8" t="inlineStr">
         <is>
-          <t>한 사람이 서는 주기</t>
+          <t>격주(교대형식)</t>
         </is>
       </c>
       <c r="P2" s="8" t="inlineStr">
         <is>
+          <t>매달</t>
+        </is>
+      </c>
+      <c r="Q2" s="8" t="inlineStr">
+        <is>
+          <t>그때그때</t>
+        </is>
+      </c>
+      <c r="R2" s="8" t="inlineStr">
+        <is>
+          <t>주일 시작 시각</t>
+        </is>
+      </c>
+      <c r="S2" s="8" t="inlineStr">
+        <is>
+          <t>주일 끝 시각</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
           <t>사역 시간·요일 (문장으로)</t>
         </is>
       </c>
-      <c r="Q2" s="8" t="inlineStr">
+      <c r="U2" s="8" t="inlineStr">
         <is>
           <t>하는 일 — 한 줄</t>
         </is>
       </c>
-      <c r="R2" s="8" t="inlineStr">
+      <c r="V2" s="8" t="inlineStr">
         <is>
           <t>필요 인원 (선택)</t>
         </is>
       </c>
-      <c r="S2" s="8" t="inlineStr">
+      <c r="W2" s="8" t="inlineStr">
         <is>
           <t>확인하신 분 (성명)</t>
         </is>
       </c>
-      <c r="T2" s="8" t="inlineStr">
+      <c r="X2" s="8" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -900,13 +927,17 @@
       <c r="K3" s="14" t="n"/>
       <c r="L3" s="14" t="n"/>
       <c r="M3" s="15" t="n"/>
-      <c r="N3" s="15" t="n"/>
-      <c r="O3" s="12" t="n"/>
-      <c r="P3" s="12" t="n"/>
-      <c r="Q3" s="12" t="n"/>
-      <c r="R3" s="12" t="n"/>
-      <c r="S3" s="12" t="n"/>
+      <c r="N3" s="14" t="n"/>
+      <c r="O3" s="15" t="n"/>
+      <c r="P3" s="14" t="n"/>
+      <c r="Q3" s="14" t="n"/>
+      <c r="R3" s="16" t="n"/>
+      <c r="S3" s="16" t="n"/>
       <c r="T3" s="12" t="n"/>
+      <c r="U3" s="12" t="n"/>
+      <c r="V3" s="12" t="n"/>
+      <c r="W3" s="12" t="n"/>
+      <c r="X3" s="12" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="9" t="n">
@@ -936,13 +967,17 @@
       <c r="K4" s="14" t="n"/>
       <c r="L4" s="14" t="n"/>
       <c r="M4" s="15" t="n"/>
-      <c r="N4" s="15" t="n"/>
-      <c r="O4" s="12" t="n"/>
-      <c r="P4" s="12" t="n"/>
-      <c r="Q4" s="12" t="n"/>
-      <c r="R4" s="12" t="n"/>
-      <c r="S4" s="12" t="n"/>
+      <c r="N4" s="14" t="n"/>
+      <c r="O4" s="15" t="n"/>
+      <c r="P4" s="14" t="n"/>
+      <c r="Q4" s="14" t="n"/>
+      <c r="R4" s="16" t="n"/>
+      <c r="S4" s="16" t="n"/>
       <c r="T4" s="12" t="n"/>
+      <c r="U4" s="12" t="n"/>
+      <c r="V4" s="12" t="n"/>
+      <c r="W4" s="12" t="n"/>
+      <c r="X4" s="12" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -972,13 +1007,17 @@
       <c r="K5" s="14" t="n"/>
       <c r="L5" s="14" t="n"/>
       <c r="M5" s="15" t="n"/>
-      <c r="N5" s="15" t="n"/>
-      <c r="O5" s="12" t="n"/>
-      <c r="P5" s="12" t="n"/>
-      <c r="Q5" s="12" t="n"/>
-      <c r="R5" s="12" t="n"/>
-      <c r="S5" s="12" t="n"/>
+      <c r="N5" s="14" t="n"/>
+      <c r="O5" s="15" t="n"/>
+      <c r="P5" s="14" t="n"/>
+      <c r="Q5" s="14" t="n"/>
+      <c r="R5" s="16" t="n"/>
+      <c r="S5" s="16" t="n"/>
       <c r="T5" s="12" t="n"/>
+      <c r="U5" s="12" t="n"/>
+      <c r="V5" s="12" t="n"/>
+      <c r="W5" s="12" t="n"/>
+      <c r="X5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -1008,13 +1047,17 @@
       <c r="K6" s="14" t="n"/>
       <c r="L6" s="14" t="n"/>
       <c r="M6" s="15" t="n"/>
-      <c r="N6" s="15" t="n"/>
-      <c r="O6" s="12" t="n"/>
-      <c r="P6" s="12" t="n"/>
-      <c r="Q6" s="12" t="n"/>
-      <c r="R6" s="12" t="n"/>
-      <c r="S6" s="12" t="n"/>
+      <c r="N6" s="14" t="n"/>
+      <c r="O6" s="15" t="n"/>
+      <c r="P6" s="14" t="n"/>
+      <c r="Q6" s="14" t="n"/>
+      <c r="R6" s="16" t="n"/>
+      <c r="S6" s="16" t="n"/>
       <c r="T6" s="12" t="n"/>
+      <c r="U6" s="12" t="n"/>
+      <c r="V6" s="12" t="n"/>
+      <c r="W6" s="12" t="n"/>
+      <c r="X6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -1044,24 +1087,28 @@
       <c r="K7" s="14" t="n"/>
       <c r="L7" s="14" t="n"/>
       <c r="M7" s="15" t="n"/>
-      <c r="N7" s="15" t="n"/>
-      <c r="O7" s="12" t="n"/>
-      <c r="P7" s="12" t="n"/>
-      <c r="Q7" s="12" t="n"/>
-      <c r="R7" s="12" t="n"/>
-      <c r="S7" s="12" t="n"/>
+      <c r="N7" s="14" t="n"/>
+      <c r="O7" s="15" t="n"/>
+      <c r="P7" s="14" t="n"/>
+      <c r="Q7" s="14" t="n"/>
+      <c r="R7" s="16" t="n"/>
+      <c r="S7" s="16" t="n"/>
       <c r="T7" s="12" t="n"/>
+      <c r="U7" s="12" t="n"/>
+      <c r="V7" s="12" t="n"/>
+      <c r="W7" s="12" t="n"/>
+      <c r="X7" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:T7"/>
+  <autoFilter ref="A2:X7"/>
   <mergeCells count="5">
-    <mergeCell ref="P1:R1"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="J1:O1"/>
-    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="T1:V1"/>
     <mergeCell ref="H1:I1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="J1:S1"/>
   </mergeCells>
-  <dataValidations count="5">
+  <dataValidations count="9">
     <dataValidation sqref="I3:I7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 골라주세요" prompt="유지 / 이름 수정 / 신설 / 폐지 중 선택" type="list">
       <formula1>"유지,이름 수정,신설,폐지"</formula1>
     </dataValidation>
@@ -1074,8 +1121,20 @@
     <dataValidation sqref="L3:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="O 만 넣어 주세요" prompt="이 요일에 사역하면 O (아니면 비워 두세요)" type="list">
       <formula1>"O"</formula1>
     </dataValidation>
-    <dataValidation sqref="O3:O7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 골라주세요" prompt="한 분이 실제로 서는 주기입니다 (팀이 모이는 주기가 아닙니다)" type="list">
-      <formula1>"매주,격주,매달,그때그때"</formula1>
+    <dataValidation sqref="M3:M7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="O 만 넣어 주세요" prompt="이 요일에 사역하면 O (아니면 비워 두세요)" type="list">
+      <formula1>"O"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N3:N7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="O 만 넣어 주세요" prompt="한 분이 실제로 서는 주기입니다 (팀이 모이는 주기가 아닙니다). 여럿이면 여럿 다 O" type="list">
+      <formula1>"O"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O3:O7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="O 만 넣어 주세요" prompt="한 분이 실제로 서는 주기입니다 (팀이 모이는 주기가 아닙니다). 여럿이면 여럿 다 O" type="list">
+      <formula1>"O"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P3:P7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="O 만 넣어 주세요" prompt="한 분이 실제로 서는 주기입니다 (팀이 모이는 주기가 아닙니다). 여럿이면 여럿 다 O" type="list">
+      <formula1>"O"</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q3:Q7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="O 만 넣어 주세요" prompt="한 분이 실제로 서는 주기입니다 (팀이 모이는 주기가 아닙니다). 여럿이면 여럿 다 O" type="list">
+      <formula1>"O"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
